--- a/data/nzd0578/nzd0578.xlsx
+++ b/data/nzd0578/nzd0578.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C415"/>
+  <dimension ref="A1:C416"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6655,6 +6655,21 @@
       <c r="C415" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:12:49+00:00</t>
+        </is>
+      </c>
+      <c r="B416" t="n">
+        <v>229.18</v>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -6669,7 +6684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B867"/>
+  <dimension ref="A1:B869"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15342,6 +15357,26 @@
       </c>
       <c r="B867" t="n">
         <v>-0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B868" t="n">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B869" t="n">
+        <v>1.13</v>
       </c>
     </row>
   </sheetData>
@@ -15504,28 +15539,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2123756419729096</v>
+        <v>0.2126369149509855</v>
       </c>
       <c r="J2" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="K2" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1457307988418743</v>
+        <v>0.1469374513676525</v>
       </c>
       <c r="M2" t="n">
-        <v>3.299561699937896</v>
+        <v>3.292556763977195</v>
       </c>
       <c r="N2" t="n">
-        <v>16.50806022232198</v>
+        <v>16.46887147731223</v>
       </c>
       <c r="O2" t="n">
-        <v>4.063011225965537</v>
+        <v>4.05818573716288</v>
       </c>
       <c r="P2" t="n">
-        <v>222.9456060536102</v>
+        <v>222.9433183760106</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -15563,7 +15598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C415"/>
+  <dimension ref="A1:C416"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22621,6 +22656,23 @@
         </is>
       </c>
     </row>
+    <row r="416">
+      <c r="A416" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:12:49+00:00</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>-41.0315564122327,173.02143623438076</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0578/nzd0578.xlsx
+++ b/data/nzd0578/nzd0578.xlsx
@@ -6684,7 +6684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B869"/>
+  <dimension ref="A1:B871"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15377,6 +15377,26 @@
       </c>
       <c r="B869" t="n">
         <v>1.13</v>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B870" t="n">
+        <v>-0.92</v>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B871" t="n">
+        <v>1.55</v>
       </c>
     </row>
   </sheetData>

--- a/data/nzd0578/nzd0578.xlsx
+++ b/data/nzd0578/nzd0578.xlsx
@@ -6684,7 +6684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B871"/>
+  <dimension ref="A1:B872"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15397,6 +15397,16 @@
       </c>
       <c r="B871" t="n">
         <v>1.55</v>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B872" t="n">
+        <v>0.9</v>
       </c>
     </row>
   </sheetData>
